--- a/sponsor_v2.xlsx
+++ b/sponsor_v2.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="12" windowWidth="16092" windowHeight="9660"/>
   </bookViews>
@@ -19,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="295">
   <si>
     <t>ID_Sponsor</t>
   </si>
@@ -69,856 +64,847 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>SPON_2021_011</t>
+  </si>
+  <si>
+    <t>SPON_2021_001</t>
+  </si>
+  <si>
+    <t>SPON_2021_007</t>
+  </si>
+  <si>
+    <t>SPON_2021_004</t>
+  </si>
+  <si>
+    <t>SPON_2021_002</t>
+  </si>
+  <si>
+    <t>SPON_2021_009</t>
+  </si>
+  <si>
+    <t>SPON_2021_006</t>
+  </si>
+  <si>
+    <t>SPON_2021_008</t>
+  </si>
+  <si>
+    <t>SPON_2021_010</t>
+  </si>
+  <si>
+    <t>SPON_2021_005</t>
+  </si>
+  <si>
+    <t>SPON_2022_020</t>
+  </si>
+  <si>
+    <t>SPON_2022_023</t>
+  </si>
+  <si>
+    <t>SPON_2022_014</t>
+  </si>
+  <si>
+    <t>SPON_2022_015</t>
+  </si>
+  <si>
+    <t>SPON_2022_013</t>
+  </si>
+  <si>
+    <t>SPON_2022_019</t>
+  </si>
+  <si>
+    <t>SPON_2022_021</t>
+  </si>
+  <si>
+    <t>SPON_2022_024</t>
+  </si>
+  <si>
+    <t>SPON_2022_017</t>
+  </si>
+  <si>
+    <t>SPON_2022_012</t>
+  </si>
+  <si>
+    <t>SPON_2022_018</t>
+  </si>
+  <si>
+    <t>SPON_2022_016</t>
+  </si>
+  <si>
+    <t>SPON_2022_022</t>
+  </si>
+  <si>
+    <t>SPON_2023_031</t>
+  </si>
+  <si>
+    <t>SPON_2023_032</t>
+  </si>
+  <si>
+    <t>SPON_2023_034</t>
+  </si>
+  <si>
+    <t>SPON_2023_029</t>
+  </si>
+  <si>
+    <t>SPON_2023_026</t>
+  </si>
+  <si>
+    <t>SPON_2023_037</t>
+  </si>
+  <si>
+    <t>SPON_2023_025</t>
+  </si>
+  <si>
+    <t>SPON_2023_027</t>
+  </si>
+  <si>
+    <t>SPON_2023_038</t>
+  </si>
+  <si>
+    <t>SPON_2023_030</t>
+  </si>
+  <si>
+    <t>SPON_2023_036</t>
+  </si>
+  <si>
+    <t>SPON_2023_028</t>
+  </si>
+  <si>
+    <t>SPON_2023_033</t>
+  </si>
+  <si>
+    <t>SPON_2023_035</t>
+  </si>
+  <si>
+    <t>SPON_2024_042</t>
+  </si>
+  <si>
+    <t>SPON_2024_047</t>
+  </si>
+  <si>
+    <t>SPON_2024_041</t>
+  </si>
+  <si>
+    <t>SPON_2024_043</t>
+  </si>
+  <si>
+    <t>SPON_2024_049</t>
+  </si>
+  <si>
+    <t>SPON_2024_048</t>
+  </si>
+  <si>
+    <t>SPON_2024_044</t>
+  </si>
+  <si>
+    <t>SPON_2024_045</t>
+  </si>
+  <si>
+    <t>SPON_2024_039</t>
+  </si>
+  <si>
+    <t>SPON_2024_040</t>
+  </si>
+  <si>
+    <t>SPON_2024_046</t>
+  </si>
+  <si>
+    <t>SPON_2025_054</t>
+  </si>
+  <si>
+    <t>SPON_2025_055</t>
+  </si>
+  <si>
+    <t>SPON_2025_056</t>
+  </si>
+  <si>
+    <t>SPON_2025_057</t>
+  </si>
+  <si>
+    <t>SPON_2025_053</t>
+  </si>
+  <si>
+    <t>SPON_2025_052</t>
+  </si>
+  <si>
+    <t>SPON_2025_051</t>
+  </si>
+  <si>
+    <t>SPON_2025_059</t>
+  </si>
+  <si>
+    <t>SPON_2025_050</t>
+  </si>
+  <si>
+    <t>SPON_2025_061</t>
+  </si>
+  <si>
+    <t>SPON_2025_058</t>
+  </si>
+  <si>
+    <t>SPON_2025_060</t>
+  </si>
+  <si>
+    <t>Tunisie Telecom</t>
+  </si>
+  <si>
+    <t>Société SFBT</t>
+  </si>
+  <si>
+    <t>Hôtel Les Jasmins</t>
+  </si>
+  <si>
+    <t>Union Européenne - Programme EU4Youth</t>
+  </si>
+  <si>
+    <t>Entreprise Familiale Ben Ahmed</t>
+  </si>
+  <si>
+    <t>Particulier - M. Salah Trabelsi</t>
+  </si>
+  <si>
+    <t>Pharmacie Centrale Korba</t>
+  </si>
+  <si>
+    <t>Restaurant Al Jazira</t>
+  </si>
+  <si>
+    <t>Magasin de Sport Champion</t>
+  </si>
+  <si>
+    <t>Coopérative Agricole</t>
+  </si>
+  <si>
+    <t>Association des Parents d'Élèves</t>
+  </si>
+  <si>
+    <t>Banque de Tunisie</t>
+  </si>
+  <si>
+    <t>Délégation Régionale Nabeul</t>
+  </si>
+  <si>
+    <t>Société de Transport Nabeul</t>
+  </si>
+  <si>
+    <t>Café des Scouts</t>
+  </si>
+  <si>
+    <t>Municipalité de Nabeul</t>
+  </si>
+  <si>
+    <t>Cabinet Médical Dr. Karim</t>
+  </si>
+  <si>
+    <t>Boulangerie Moderne</t>
+  </si>
+  <si>
+    <t>ONG Jeunesse et Avenir</t>
+  </si>
+  <si>
+    <t>Fondation Nationale pour le Développement</t>
+  </si>
+  <si>
+    <t>Agence Tunisienne de Coopération</t>
+  </si>
+  <si>
+    <t>Ministère de la Jeunesse</t>
+  </si>
+  <si>
+    <t>Société Tunisienne des Industries Textiles</t>
+  </si>
+  <si>
+    <t>Agence de Voyage Découverte</t>
+  </si>
+  <si>
+    <t>Particulier - Mme Leila Mansouri</t>
+  </si>
+  <si>
+    <t>Entreprise SONEDE</t>
+  </si>
+  <si>
+    <t>Librairie Scolaire</t>
+  </si>
+  <si>
+    <t>Entreprise</t>
+  </si>
+  <si>
+    <t>International</t>
+  </si>
+  <si>
+    <t>Particulier</t>
+  </si>
+  <si>
+    <t>ONG</t>
+  </si>
+  <si>
+    <t>Gouvernement</t>
+  </si>
+  <si>
+    <t>Social</t>
+  </si>
+  <si>
+    <t>Sport</t>
+  </si>
+  <si>
+    <t>Environnement</t>
+  </si>
+  <si>
+    <t>Culture</t>
+  </si>
+  <si>
+    <t>Éducation</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
+    <t>Général</t>
+  </si>
+  <si>
+    <t>Nourriture pour camps</t>
+  </si>
+  <si>
+    <t>Santé et sécurité</t>
+  </si>
+  <si>
+    <t>Transport pour sorties</t>
+  </si>
+  <si>
+    <t>Projet communautaire</t>
+  </si>
+  <si>
+    <t>Matériel pédagogique</t>
+  </si>
+  <si>
+    <t>Activités culturelles</t>
+  </si>
+  <si>
+    <t>Sortie éducative</t>
+  </si>
+  <si>
+    <t>Équipement sportif</t>
+  </si>
+  <si>
+    <t>Camp d'été</t>
+  </si>
+  <si>
+    <t>Soutien général</t>
+  </si>
+  <si>
+    <t>Activités environnementales</t>
+  </si>
+  <si>
+    <t>Camp de printemps</t>
+  </si>
+  <si>
+    <t>Formation des chefs</t>
+  </si>
+  <si>
+    <t>Uniforme scouts</t>
+  </si>
+  <si>
+    <t>Rénovation local</t>
+  </si>
+  <si>
+    <t>الكشافة</t>
+  </si>
+  <si>
+    <t>الزهرات</t>
+  </si>
+  <si>
+    <t>الأشبال</t>
+  </si>
+  <si>
+    <t>الجوالة</t>
+  </si>
+  <si>
+    <t>المرشدات</t>
+  </si>
+  <si>
+    <t>العصافير</t>
+  </si>
+  <si>
+    <t>2021-2022</t>
+  </si>
+  <si>
+    <t>2022-2023</t>
+  </si>
+  <si>
+    <t>2023-2024</t>
+  </si>
+  <si>
+    <t>2024-2025</t>
+  </si>
+  <si>
+    <t>2025-2026</t>
+  </si>
+  <si>
+    <t>05/01/2022</t>
+  </si>
+  <si>
+    <t>07/06/2021</t>
+  </si>
+  <si>
+    <t>08/04/2022</t>
+  </si>
+  <si>
+    <t>09/09/2021</t>
+  </si>
+  <si>
+    <t>11/04/2022</t>
+  </si>
+  <si>
+    <t>11/12/2021</t>
+  </si>
+  <si>
+    <t>12/09/2021</t>
+  </si>
+  <si>
+    <t>13/03/2022</t>
+  </si>
+  <si>
+    <t>16/11/2021</t>
+  </si>
+  <si>
+    <t>28/12/2021</t>
+  </si>
+  <si>
+    <t>05/03/2023</t>
+  </si>
+  <si>
+    <t>06/10/2022</t>
+  </si>
+  <si>
+    <t>07/03/2023</t>
+  </si>
+  <si>
+    <t>08/07/2022</t>
+  </si>
+  <si>
+    <t>16/09/2022</t>
+  </si>
+  <si>
+    <t>17/04/2023</t>
+  </si>
+  <si>
+    <t>22/01/2023</t>
+  </si>
+  <si>
+    <t>24/03/2023</t>
+  </si>
+  <si>
+    <t>29/09/2022</t>
+  </si>
+  <si>
+    <t>30/07/2022</t>
+  </si>
+  <si>
+    <t>30/10/2022</t>
+  </si>
+  <si>
+    <t>31/12/2022</t>
+  </si>
+  <si>
+    <t>01/09/2023</t>
+  </si>
+  <si>
+    <t>02/09/2023</t>
+  </si>
+  <si>
+    <t>02/12/2023</t>
+  </si>
+  <si>
+    <t>06/10/2023</t>
+  </si>
+  <si>
+    <t>08/02/2024</t>
+  </si>
+  <si>
+    <t>12/10/2023</t>
+  </si>
+  <si>
+    <t>18/11/2023</t>
+  </si>
+  <si>
+    <t>21/06/2023</t>
+  </si>
+  <si>
+    <t>21/10/2023</t>
+  </si>
+  <si>
+    <t>21/11/2023</t>
+  </si>
+  <si>
+    <t>23/12/2023</t>
+  </si>
+  <si>
+    <t>27/10/2023</t>
+  </si>
+  <si>
+    <t>05/05/2025</t>
+  </si>
+  <si>
+    <t>11/12/2024</t>
+  </si>
+  <si>
+    <t>14/05/2025</t>
+  </si>
+  <si>
+    <t>15/07/2024</t>
+  </si>
+  <si>
+    <t>20/10/2024</t>
+  </si>
+  <si>
+    <t>24/04/2025</t>
+  </si>
+  <si>
+    <t>25/11/2024</t>
+  </si>
+  <si>
+    <t>28/01/2025</t>
+  </si>
+  <si>
+    <t>28/08/2024</t>
+  </si>
+  <si>
+    <t>28/12/2024</t>
+  </si>
+  <si>
+    <t>29/12/2024</t>
+  </si>
+  <si>
+    <t>05/04/2026</t>
+  </si>
+  <si>
+    <t>07/08/2025</t>
+  </si>
+  <si>
+    <t>07/12/2025</t>
+  </si>
+  <si>
+    <t>14/12/2025</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>18/08/2025</t>
+  </si>
+  <si>
+    <t>20/04/2026</t>
+  </si>
+  <si>
+    <t>23/11/2025</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>25/08/2025</t>
+  </si>
+  <si>
+    <t>28/12/2025</t>
+  </si>
+  <si>
+    <t>29/03/2026</t>
+  </si>
+  <si>
+    <t>31/12/2021</t>
+  </si>
+  <si>
+    <t>27/02/2022</t>
+  </si>
+  <si>
+    <t>05/09/2021</t>
+  </si>
+  <si>
+    <t>28/05/2022</t>
+  </si>
+  <si>
+    <t>06/12/2021</t>
+  </si>
+  <si>
+    <t>30/06/2022</t>
+  </si>
+  <si>
+    <t>25/11/2021</t>
+  </si>
+  <si>
+    <t>07/06/2022</t>
+  </si>
+  <si>
+    <t>06/01/2022</t>
+  </si>
+  <si>
+    <t>08/02/2022</t>
+  </si>
+  <si>
+    <t>27/05/2023</t>
+  </si>
+  <si>
+    <t>03/12/2022</t>
+  </si>
+  <si>
+    <t>12/05/2023</t>
+  </si>
+  <si>
+    <t>11/09/2022</t>
+  </si>
+  <si>
+    <t>29/10/2022</t>
+  </si>
+  <si>
+    <t>02/06/2023</t>
+  </si>
+  <si>
+    <t>21/04/2023</t>
+  </si>
+  <si>
+    <t>25/04/2023</t>
+  </si>
+  <si>
+    <t>24/11/2022</t>
+  </si>
+  <si>
+    <t>02/09/2022</t>
+  </si>
+  <si>
+    <t>24/10/2022</t>
+  </si>
+  <si>
+    <t>18/12/2022</t>
+  </si>
+  <si>
+    <t>02/02/2023</t>
+  </si>
+  <si>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>17/10/2023</t>
+  </si>
+  <si>
+    <t>23/02/2024</t>
+  </si>
+  <si>
+    <t>10/11/2023</t>
+  </si>
+  <si>
+    <t>11/01/2024</t>
+  </si>
+  <si>
+    <t>07/10/2023</t>
+  </si>
+  <si>
+    <t>22/01/2024</t>
+  </si>
+  <si>
+    <t>07/09/2023</t>
+  </si>
+  <si>
+    <t>10/01/2024</t>
+  </si>
+  <si>
+    <t>15/02/2024</t>
+  </si>
+  <si>
+    <t>20/01/2024</t>
+  </si>
+  <si>
+    <t>25/06/2025</t>
+  </si>
+  <si>
+    <t>22/02/2025</t>
+  </si>
+  <si>
+    <t>15/06/2025</t>
+  </si>
+  <si>
+    <t>05/10/2024</t>
+  </si>
+  <si>
+    <t>27/11/2024</t>
+  </si>
+  <si>
+    <t>16/06/2025</t>
+  </si>
+  <si>
+    <t>01/01/2025</t>
+  </si>
+  <si>
+    <t>26/04/2025</t>
+  </si>
+  <si>
+    <t>16/11/2024</t>
+  </si>
+  <si>
+    <t>03/03/2025</t>
+  </si>
+  <si>
+    <t>21/03/2025</t>
+  </si>
+  <si>
+    <t>06/05/2026</t>
+  </si>
+  <si>
+    <t>17/10/2025</t>
+  </si>
+  <si>
+    <t>10/01/2026</t>
+  </si>
+  <si>
+    <t>14/01/2026</t>
+  </si>
+  <si>
+    <t>10/06/2026</t>
+  </si>
+  <si>
+    <t>05/11/2025</t>
+  </si>
+  <si>
+    <t>03/06/2026</t>
+  </si>
+  <si>
+    <t>22/01/2026</t>
+  </si>
+  <si>
+    <t>23/05/2026</t>
+  </si>
+  <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>30/05/2026</t>
+  </si>
+  <si>
+    <t>Partiel</t>
+  </si>
+  <si>
+    <t>Reçu</t>
+  </si>
+  <si>
+    <t>Promis</t>
+  </si>
+  <si>
+    <t>Camp printemps</t>
+  </si>
+  <si>
+    <t>Camp été</t>
+  </si>
+  <si>
+    <t>Formation</t>
+  </si>
+  <si>
+    <t>Équipement</t>
+  </si>
+  <si>
+    <t>Activités</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Nourriture</t>
+  </si>
+  <si>
+    <t>Uniforme</t>
+  </si>
+  <si>
+    <t>Sousse</t>
+  </si>
+  <si>
+    <t>Ariana</t>
+  </si>
+  <si>
+    <t>Tunis</t>
+  </si>
+  <si>
+    <t>Nabeul</t>
+  </si>
+  <si>
+    <t>Ben Arous</t>
+  </si>
+  <si>
+    <t>Monastir</t>
+  </si>
+  <si>
+    <t>Sfax</t>
+  </si>
+  <si>
+    <t>Convention signée le 01/12/2021</t>
+  </si>
+  <si>
+    <t>Renouvellement prévu l'année prochaine</t>
+  </si>
+  <si>
+    <t>Premier partenariat</t>
+  </si>
+  <si>
+    <t>Contact: contact@sponsor.tn</t>
+  </si>
+  <si>
+    <t>Convention signée le 16/11/2021</t>
+  </si>
+  <si>
+    <t>Sponsor récurrent</t>
+  </si>
+  <si>
+    <t>Convention signée le 06/10/2022</t>
+  </si>
+  <si>
+    <t>Convention signée le 24/03/2023</t>
+  </si>
+  <si>
+    <t>Convention signée le 30/07/2022</t>
+  </si>
+  <si>
+    <t>Convention signée le 08/02/2024</t>
+  </si>
+  <si>
+    <t>Convention signée le 28/08/2024</t>
+  </si>
+  <si>
+    <t>Convention signée le 20/04/2026</t>
+  </si>
+  <si>
+    <t>Code_lieu</t>
+  </si>
+  <si>
+    <t>SSE</t>
+  </si>
+  <si>
+    <t>ARN</t>
+  </si>
+  <si>
+    <t>TNS</t>
+  </si>
+  <si>
+    <t>SFX</t>
+  </si>
+  <si>
+    <t>NBL</t>
+  </si>
+  <si>
+    <t>BRS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARN </t>
+  </si>
+  <si>
+    <t>MST</t>
+  </si>
+  <si>
     <t>SPON_2021_003</t>
   </si>
   <si>
-    <t>SPON_2021_011</t>
-  </si>
-  <si>
-    <t>SPON_2021_001</t>
-  </si>
-  <si>
-    <t>SPON_2021_007</t>
-  </si>
-  <si>
-    <t>SPON_2021_004</t>
-  </si>
-  <si>
-    <t>SPON_2021_002</t>
-  </si>
-  <si>
-    <t>SPON_2021_009</t>
-  </si>
-  <si>
-    <t>SPON_2021_006</t>
-  </si>
-  <si>
-    <t>SPON_2021_008</t>
-  </si>
-  <si>
-    <t>SPON_2021_010</t>
-  </si>
-  <si>
-    <t>SPON_2021_005</t>
-  </si>
-  <si>
-    <t>SPON_2022_020</t>
-  </si>
-  <si>
-    <t>SPON_2022_023</t>
-  </si>
-  <si>
-    <t>SPON_2022_014</t>
-  </si>
-  <si>
-    <t>SPON_2022_015</t>
-  </si>
-  <si>
-    <t>SPON_2022_013</t>
-  </si>
-  <si>
-    <t>SPON_2022_019</t>
-  </si>
-  <si>
-    <t>SPON_2022_021</t>
-  </si>
-  <si>
-    <t>SPON_2022_024</t>
-  </si>
-  <si>
-    <t>SPON_2022_017</t>
-  </si>
-  <si>
-    <t>SPON_2022_012</t>
-  </si>
-  <si>
-    <t>SPON_2022_018</t>
-  </si>
-  <si>
-    <t>SPON_2022_016</t>
-  </si>
-  <si>
-    <t>SPON_2022_022</t>
-  </si>
-  <si>
-    <t>SPON_2023_031</t>
-  </si>
-  <si>
-    <t>SPON_2023_032</t>
-  </si>
-  <si>
-    <t>SPON_2023_034</t>
-  </si>
-  <si>
-    <t>SPON_2023_029</t>
-  </si>
-  <si>
-    <t>SPON_2023_026</t>
-  </si>
-  <si>
-    <t>SPON_2023_037</t>
-  </si>
-  <si>
-    <t>SPON_2023_025</t>
-  </si>
-  <si>
-    <t>SPON_2023_027</t>
-  </si>
-  <si>
-    <t>SPON_2023_038</t>
-  </si>
-  <si>
-    <t>SPON_2023_030</t>
-  </si>
-  <si>
-    <t>SPON_2023_036</t>
-  </si>
-  <si>
-    <t>SPON_2023_028</t>
-  </si>
-  <si>
-    <t>SPON_2023_033</t>
-  </si>
-  <si>
-    <t>SPON_2023_035</t>
-  </si>
-  <si>
-    <t>SPON_2024_042</t>
-  </si>
-  <si>
-    <t>SPON_2024_047</t>
-  </si>
-  <si>
-    <t>SPON_2024_041</t>
-  </si>
-  <si>
-    <t>SPON_2024_043</t>
-  </si>
-  <si>
-    <t>SPON_2024_049</t>
-  </si>
-  <si>
-    <t>SPON_2024_048</t>
-  </si>
-  <si>
-    <t>SPON_2024_044</t>
-  </si>
-  <si>
-    <t>SPON_2024_045</t>
-  </si>
-  <si>
-    <t>SPON_2024_039</t>
-  </si>
-  <si>
-    <t>SPON_2024_040</t>
-  </si>
-  <si>
-    <t>SPON_2024_046</t>
-  </si>
-  <si>
-    <t>SPON_2025_054</t>
-  </si>
-  <si>
-    <t>SPON_2025_055</t>
-  </si>
-  <si>
-    <t>SPON_2025_056</t>
-  </si>
-  <si>
-    <t>SPON_2025_057</t>
-  </si>
-  <si>
-    <t>SPON_2025_053</t>
-  </si>
-  <si>
-    <t>SPON_2025_052</t>
-  </si>
-  <si>
-    <t>SPON_2025_051</t>
-  </si>
-  <si>
-    <t>SPON_2025_059</t>
-  </si>
-  <si>
-    <t>SPON_2025_050</t>
-  </si>
-  <si>
-    <t>SPON_2025_061</t>
-  </si>
-  <si>
-    <t>SPON_2025_058</t>
-  </si>
-  <si>
-    <t>SPON_2025_060</t>
-  </si>
-  <si>
-    <t>Tunisie Telecom</t>
-  </si>
-  <si>
-    <t>Société SFBT</t>
-  </si>
-  <si>
-    <t>Hôtel Les Jasmins</t>
-  </si>
-  <si>
-    <t>Union Européenne - Programme EU4Youth</t>
-  </si>
-  <si>
-    <t>Entreprise Familiale Ben Ahmed</t>
-  </si>
-  <si>
-    <t>Particulier - M. Salah Trabelsi</t>
-  </si>
-  <si>
-    <t>Pharmacie Centrale Korba</t>
-  </si>
-  <si>
-    <t>Restaurant Al Jazira</t>
-  </si>
-  <si>
-    <t>Magasin de Sport Champion</t>
-  </si>
-  <si>
-    <t>Coopérative Agricole</t>
-  </si>
-  <si>
-    <t>Association des Parents d'Élèves</t>
-  </si>
-  <si>
-    <t>Banque de Tunisie</t>
-  </si>
-  <si>
-    <t>Délégation Régionale Nabeul</t>
-  </si>
-  <si>
-    <t>Société de Transport Nabeul</t>
-  </si>
-  <si>
-    <t>Café des Scouts</t>
-  </si>
-  <si>
-    <t>Municipalité de Nabeul</t>
-  </si>
-  <si>
-    <t>Cabinet Médical Dr. Karim</t>
-  </si>
-  <si>
-    <t>Boulangerie Moderne</t>
-  </si>
-  <si>
-    <t>ONG Jeunesse et Avenir</t>
-  </si>
-  <si>
-    <t>Fondation Nationale pour le Développement</t>
-  </si>
-  <si>
-    <t>Agence Tunisienne de Coopération</t>
-  </si>
-  <si>
-    <t>Ministère de la Jeunesse</t>
-  </si>
-  <si>
-    <t>Société Tunisienne des Industries Textiles</t>
-  </si>
-  <si>
-    <t>Agence de Voyage Découverte</t>
-  </si>
-  <si>
-    <t>Particulier - Mme Leila Mansouri</t>
-  </si>
-  <si>
-    <t>Entreprise SONEDE</t>
-  </si>
-  <si>
-    <t>Librairie Scolaire</t>
-  </si>
-  <si>
-    <t>Entreprise</t>
-  </si>
-  <si>
-    <t>International</t>
-  </si>
-  <si>
-    <t>Particulier</t>
-  </si>
-  <si>
-    <t>ONG</t>
-  </si>
-  <si>
-    <t>Gouvernement</t>
-  </si>
-  <si>
-    <t>Social</t>
-  </si>
-  <si>
-    <t>Sport</t>
-  </si>
-  <si>
-    <t>Environnement</t>
-  </si>
-  <si>
-    <t>Culture</t>
-  </si>
-  <si>
-    <t>Éducation</t>
-  </si>
-  <si>
-    <t>Santé</t>
-  </si>
-  <si>
-    <t>Général</t>
-  </si>
-  <si>
-    <t>Nourriture pour camps</t>
-  </si>
-  <si>
-    <t>Santé et sécurité</t>
-  </si>
-  <si>
-    <t>Transport pour sorties</t>
-  </si>
-  <si>
-    <t>Projet communautaire</t>
-  </si>
-  <si>
-    <t>Matériel pédagogique</t>
-  </si>
-  <si>
-    <t>Activités culturelles</t>
-  </si>
-  <si>
-    <t>Sortie éducative</t>
-  </si>
-  <si>
-    <t>Équipement sportif</t>
-  </si>
-  <si>
-    <t>Camp d'été</t>
-  </si>
-  <si>
-    <t>Soutien général</t>
-  </si>
-  <si>
-    <t>Activités environnementales</t>
-  </si>
-  <si>
-    <t>Camp de printemps</t>
-  </si>
-  <si>
-    <t>Formation des chefs</t>
-  </si>
-  <si>
-    <t>Uniforme scouts</t>
-  </si>
-  <si>
-    <t>Rénovation local</t>
-  </si>
-  <si>
-    <t>الكشافة</t>
-  </si>
-  <si>
-    <t>الزهرات</t>
-  </si>
-  <si>
-    <t>الأشبال</t>
-  </si>
-  <si>
-    <t>الجوالة</t>
-  </si>
-  <si>
-    <t>المرشدات</t>
-  </si>
-  <si>
-    <t>العصافير</t>
-  </si>
-  <si>
-    <t>2021-2022</t>
-  </si>
-  <si>
-    <t>2022-2023</t>
-  </si>
-  <si>
-    <t>2023-2024</t>
-  </si>
-  <si>
-    <t>2024-2025</t>
-  </si>
-  <si>
-    <t>2025-2026</t>
-  </si>
-  <si>
-    <t>01/12/2021</t>
-  </si>
-  <si>
-    <t>05/01/2022</t>
-  </si>
-  <si>
-    <t>07/06/2021</t>
-  </si>
-  <si>
-    <t>08/04/2022</t>
-  </si>
-  <si>
-    <t>09/09/2021</t>
-  </si>
-  <si>
-    <t>11/04/2022</t>
-  </si>
-  <si>
-    <t>11/12/2021</t>
-  </si>
-  <si>
-    <t>12/09/2021</t>
-  </si>
-  <si>
-    <t>13/03/2022</t>
-  </si>
-  <si>
-    <t>16/11/2021</t>
-  </si>
-  <si>
-    <t>28/12/2021</t>
-  </si>
-  <si>
-    <t>05/03/2023</t>
-  </si>
-  <si>
-    <t>06/10/2022</t>
-  </si>
-  <si>
-    <t>07/03/2023</t>
-  </si>
-  <si>
-    <t>08/07/2022</t>
-  </si>
-  <si>
-    <t>16/09/2022</t>
-  </si>
-  <si>
-    <t>17/04/2023</t>
-  </si>
-  <si>
-    <t>22/01/2023</t>
-  </si>
-  <si>
-    <t>24/03/2023</t>
-  </si>
-  <si>
-    <t>29/09/2022</t>
-  </si>
-  <si>
-    <t>30/07/2022</t>
-  </si>
-  <si>
-    <t>30/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
-    <t>01/09/2023</t>
-  </si>
-  <si>
-    <t>02/09/2023</t>
-  </si>
-  <si>
-    <t>02/12/2023</t>
-  </si>
-  <si>
-    <t>06/10/2023</t>
-  </si>
-  <si>
-    <t>08/02/2024</t>
-  </si>
-  <si>
-    <t>12/10/2023</t>
-  </si>
-  <si>
-    <t>12/12/2023</t>
-  </si>
-  <si>
-    <t>18/07/2023</t>
-  </si>
-  <si>
-    <t>18/11/2023</t>
-  </si>
-  <si>
-    <t>21/06/2023</t>
-  </si>
-  <si>
-    <t>21/10/2023</t>
-  </si>
-  <si>
-    <t>21/11/2023</t>
-  </si>
-  <si>
-    <t>23/12/2023</t>
-  </si>
-  <si>
-    <t>27/10/2023</t>
-  </si>
-  <si>
-    <t>05/05/2025</t>
-  </si>
-  <si>
-    <t>11/12/2024</t>
-  </si>
-  <si>
-    <t>14/05/2025</t>
-  </si>
-  <si>
-    <t>15/07/2024</t>
-  </si>
-  <si>
-    <t>20/10/2024</t>
-  </si>
-  <si>
-    <t>24/04/2025</t>
-  </si>
-  <si>
-    <t>25/11/2024</t>
-  </si>
-  <si>
-    <t>28/01/2025</t>
-  </si>
-  <si>
-    <t>28/08/2024</t>
-  </si>
-  <si>
-    <t>28/12/2024</t>
-  </si>
-  <si>
-    <t>29/12/2024</t>
-  </si>
-  <si>
-    <t>05/04/2026</t>
-  </si>
-  <si>
-    <t>07/08/2025</t>
-  </si>
-  <si>
-    <t>07/12/2025</t>
-  </si>
-  <si>
-    <t>14/12/2025</t>
-  </si>
-  <si>
-    <t>18/03/2026</t>
-  </si>
-  <si>
-    <t>18/08/2025</t>
-  </si>
-  <si>
-    <t>20/04/2026</t>
-  </si>
-  <si>
-    <t>23/11/2025</t>
-  </si>
-  <si>
-    <t>25/03/2026</t>
-  </si>
-  <si>
-    <t>25/08/2025</t>
-  </si>
-  <si>
-    <t>28/12/2025</t>
-  </si>
-  <si>
-    <t>29/03/2026</t>
-  </si>
-  <si>
-    <t>31/12/2021</t>
-  </si>
-  <si>
-    <t>27/02/2022</t>
-  </si>
-  <si>
-    <t>05/09/2021</t>
-  </si>
-  <si>
-    <t>28/05/2022</t>
-  </si>
-  <si>
-    <t>06/12/2021</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>25/11/2021</t>
-  </si>
-  <si>
-    <t>07/06/2022</t>
-  </si>
-  <si>
-    <t>06/01/2022</t>
-  </si>
-  <si>
-    <t>08/02/2022</t>
-  </si>
-  <si>
-    <t>27/05/2023</t>
-  </si>
-  <si>
-    <t>03/12/2022</t>
-  </si>
-  <si>
-    <t>12/05/2023</t>
-  </si>
-  <si>
-    <t>11/09/2022</t>
-  </si>
-  <si>
-    <t>29/10/2022</t>
-  </si>
-  <si>
-    <t>02/06/2023</t>
-  </si>
-  <si>
-    <t>21/04/2023</t>
-  </si>
-  <si>
-    <t>25/04/2023</t>
-  </si>
-  <si>
-    <t>24/11/2022</t>
-  </si>
-  <si>
-    <t>02/09/2022</t>
-  </si>
-  <si>
-    <t>24/10/2022</t>
-  </si>
-  <si>
-    <t>18/12/2022</t>
-  </si>
-  <si>
-    <t>02/02/2023</t>
-  </si>
-  <si>
-    <t>01/10/2023</t>
-  </si>
-  <si>
-    <t>17/10/2023</t>
-  </si>
-  <si>
-    <t>23/02/2024</t>
-  </si>
-  <si>
-    <t>10/11/2023</t>
-  </si>
-  <si>
-    <t>25/03/2024</t>
-  </si>
-  <si>
-    <t>11/01/2024</t>
-  </si>
-  <si>
-    <t>07/10/2023</t>
-  </si>
-  <si>
-    <t>22/01/2024</t>
-  </si>
-  <si>
-    <t>07/09/2023</t>
-  </si>
-  <si>
-    <t>10/01/2024</t>
-  </si>
-  <si>
-    <t>15/02/2024</t>
-  </si>
-  <si>
-    <t>20/01/2024</t>
-  </si>
-  <si>
-    <t>25/06/2025</t>
-  </si>
-  <si>
-    <t>22/02/2025</t>
-  </si>
-  <si>
-    <t>15/06/2025</t>
-  </si>
-  <si>
-    <t>05/10/2024</t>
-  </si>
-  <si>
-    <t>27/11/2024</t>
-  </si>
-  <si>
-    <t>16/06/2025</t>
-  </si>
-  <si>
-    <t>01/01/2025</t>
-  </si>
-  <si>
-    <t>26/04/2025</t>
-  </si>
-  <si>
-    <t>16/11/2024</t>
-  </si>
-  <si>
-    <t>03/03/2025</t>
-  </si>
-  <si>
-    <t>21/03/2025</t>
-  </si>
-  <si>
-    <t>06/05/2026</t>
-  </si>
-  <si>
-    <t>17/10/2025</t>
-  </si>
-  <si>
-    <t>10/01/2026</t>
-  </si>
-  <si>
-    <t>14/01/2026</t>
-  </si>
-  <si>
-    <t>10/06/2026</t>
-  </si>
-  <si>
-    <t>05/11/2025</t>
-  </si>
-  <si>
-    <t>03/06/2026</t>
-  </si>
-  <si>
-    <t>22/01/2026</t>
-  </si>
-  <si>
-    <t>23/05/2026</t>
-  </si>
-  <si>
-    <t>20/02/2026</t>
-  </si>
-  <si>
-    <t>30/05/2026</t>
-  </si>
-  <si>
-    <t>Partiel</t>
-  </si>
-  <si>
-    <t>Reçu</t>
-  </si>
-  <si>
-    <t>Promis</t>
-  </si>
-  <si>
-    <t>Camp printemps</t>
-  </si>
-  <si>
-    <t>Camp été</t>
-  </si>
-  <si>
-    <t>Formation</t>
-  </si>
-  <si>
-    <t>Équipement</t>
-  </si>
-  <si>
-    <t>Activités</t>
-  </si>
-  <si>
-    <t>Transport</t>
-  </si>
-  <si>
-    <t>Nourriture</t>
-  </si>
-  <si>
-    <t>Uniforme</t>
-  </si>
-  <si>
-    <t>Sousse</t>
-  </si>
-  <si>
-    <t>Ariana</t>
-  </si>
-  <si>
-    <t>Tunis</t>
-  </si>
-  <si>
-    <t>Nabeul</t>
-  </si>
-  <si>
-    <t>Ben Arous</t>
-  </si>
-  <si>
-    <t>Monastir</t>
-  </si>
-  <si>
-    <t>Sfax</t>
-  </si>
-  <si>
-    <t>Convention signée le 01/12/2021</t>
-  </si>
-  <si>
-    <t>Renouvellement prévu l'année prochaine</t>
-  </si>
-  <si>
-    <t>Premier partenariat</t>
-  </si>
-  <si>
-    <t>Contact: contact@sponsor.tn</t>
-  </si>
-  <si>
-    <t>Convention signée le 16/11/2021</t>
-  </si>
-  <si>
-    <t>Sponsor récurrent</t>
-  </si>
-  <si>
-    <t>Convention signée le 06/10/2022</t>
-  </si>
-  <si>
-    <t>Convention signée le 24/03/2023</t>
-  </si>
-  <si>
-    <t>Convention signée le 30/07/2022</t>
-  </si>
-  <si>
-    <t>Convention signée le 08/02/2024</t>
-  </si>
-  <si>
-    <t>Convention signée le 28/08/2024</t>
-  </si>
-  <si>
-    <t>Convention signée le 20/04/2026</t>
-  </si>
-  <si>
-    <t>Code_lieu</t>
-  </si>
-  <si>
-    <t>SSE</t>
-  </si>
-  <si>
-    <t>ARN</t>
-  </si>
-  <si>
-    <t>TNS</t>
-  </si>
-  <si>
-    <t>SFX</t>
-  </si>
-  <si>
-    <t>NBL</t>
-  </si>
-  <si>
-    <t>BRS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARN </t>
-  </si>
-  <si>
-    <t>MST</t>
+    <t>20/15/2021</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -968,7 +954,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1010,7 +996,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1045,7 +1031,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1255,16 +1241,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q62"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="3" max="3" width="39.21875" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" customWidth="1"/>
     <col min="6" max="6" width="22.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="16.109375" customWidth="1"/>
     <col min="10" max="10" width="17.21875" customWidth="1"/>
     <col min="11" max="11" width="15.21875" customWidth="1"/>
     <col min="12" max="12" width="16.21875" customWidth="1"/>
     <col min="14" max="14" width="19.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
@@ -1311,7 +1301,7 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="P1" t="s">
         <v>14</v>
@@ -1325,31 +1315,31 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>293</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I2" t="s">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="J2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K2">
         <v>7898</v>
@@ -1358,19 +1348,19 @@
         <v>3217</v>
       </c>
       <c r="M2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="N2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="Q2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -1378,31 +1368,31 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="J3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K3">
         <v>5069</v>
@@ -1411,16 +1401,16 @@
         <v>5069</v>
       </c>
       <c r="M3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="P3" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
@@ -1428,31 +1418,31 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="K4">
         <v>2016</v>
@@ -1461,16 +1451,16 @@
         <v>2016</v>
       </c>
       <c r="M4" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N4" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="O4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P4" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
@@ -1478,31 +1468,31 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="K5">
         <v>20563</v>
@@ -1511,19 +1501,19 @@
         <v>20563</v>
       </c>
       <c r="M5" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N5" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="O5" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P5" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="Q5" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -1531,31 +1521,31 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J6" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="K6">
         <v>8794</v>
@@ -1564,19 +1554,19 @@
         <v>8794</v>
       </c>
       <c r="M6" t="s">
+        <v>255</v>
+      </c>
+      <c r="N6" t="s">
         <v>260</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
+        <v>285</v>
+      </c>
+      <c r="P6" t="s">
         <v>265</v>
       </c>
-      <c r="O6" t="s">
-        <v>290</v>
-      </c>
-      <c r="P6" t="s">
-        <v>270</v>
-      </c>
       <c r="Q6" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
@@ -1584,31 +1574,31 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J7" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="K7">
         <v>1472</v>
@@ -1617,16 +1607,16 @@
         <v>1472</v>
       </c>
       <c r="M7" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N7" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O7" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P7" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -1634,28 +1624,31 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I8" t="s">
-        <v>148</v>
+        <v>146</v>
+      </c>
+      <c r="J8" t="s">
+        <v>294</v>
       </c>
       <c r="K8">
         <v>5592</v>
@@ -1664,16 +1657,16 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="N8" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O8" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P8" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -1681,31 +1674,31 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="K9">
         <v>3756</v>
@@ -1714,19 +1707,19 @@
         <v>1607</v>
       </c>
       <c r="M9" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="N9" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O9" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P9" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="Q9" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -1734,31 +1727,31 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J10" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="K10">
         <v>9844</v>
@@ -1767,19 +1760,19 @@
         <v>9844</v>
       </c>
       <c r="M10" t="s">
+        <v>255</v>
+      </c>
+      <c r="N10" t="s">
         <v>260</v>
       </c>
-      <c r="N10" t="s">
-        <v>265</v>
-      </c>
       <c r="O10" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P10" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="Q10" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -1787,31 +1780,31 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J11" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="K11">
         <v>6889</v>
@@ -1820,19 +1813,19 @@
         <v>6889</v>
       </c>
       <c r="M11" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N11" t="s">
+        <v>261</v>
+      </c>
+      <c r="O11" t="s">
+        <v>286</v>
+      </c>
+      <c r="P11" t="s">
         <v>266</v>
       </c>
-      <c r="O11" t="s">
-        <v>291</v>
-      </c>
-      <c r="P11" t="s">
-        <v>271</v>
-      </c>
       <c r="Q11" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -1840,31 +1833,31 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I12" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J12" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="K12">
         <v>7380</v>
@@ -1873,19 +1866,19 @@
         <v>3784</v>
       </c>
       <c r="M12" t="s">
+        <v>254</v>
+      </c>
+      <c r="N12" t="s">
         <v>259</v>
       </c>
-      <c r="N12" t="s">
-        <v>264</v>
-      </c>
       <c r="O12" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P12" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="Q12" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
@@ -1893,31 +1886,31 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J13" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K13">
         <v>6469</v>
@@ -1926,19 +1919,19 @@
         <v>6469</v>
       </c>
       <c r="M13" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O13" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="P13" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="Q13" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
@@ -1946,31 +1939,31 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I14" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J14" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="K14">
         <v>2936</v>
@@ -1979,19 +1972,19 @@
         <v>2936</v>
       </c>
       <c r="M14" t="s">
+        <v>255</v>
+      </c>
+      <c r="N14" t="s">
         <v>260</v>
       </c>
-      <c r="N14" t="s">
-        <v>265</v>
-      </c>
       <c r="O14" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="P14" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="Q14" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -1999,31 +1992,31 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I15" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J15" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="K15">
         <v>9205</v>
@@ -2032,16 +2025,16 @@
         <v>9205</v>
       </c>
       <c r="M15" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N15" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="O15" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="P15" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -2049,31 +2042,31 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J16" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="K16">
         <v>11709</v>
@@ -2082,16 +2075,16 @@
         <v>9088</v>
       </c>
       <c r="M16" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="N16" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="O16" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="P16" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
@@ -2099,31 +2092,31 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J17" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K17">
         <v>5771</v>
@@ -2132,16 +2125,16 @@
         <v>5771</v>
       </c>
       <c r="M17" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O17" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P17" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
@@ -2149,31 +2142,31 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J18" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="K18">
         <v>6202</v>
@@ -2182,19 +2175,19 @@
         <v>6202</v>
       </c>
       <c r="M18" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N18" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="O18" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P18" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Q18" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -2202,31 +2195,31 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J19" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="K19">
         <v>11928</v>
@@ -2235,16 +2228,16 @@
         <v>11928</v>
       </c>
       <c r="M19" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N19" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="O19" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="P19" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
@@ -2252,31 +2245,31 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J20" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="K20">
         <v>2323</v>
@@ -2285,19 +2278,19 @@
         <v>1618</v>
       </c>
       <c r="M20" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="N20" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="O20" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P20" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Q20" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
@@ -2305,31 +2298,31 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H21" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I21" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="J21" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K21">
         <v>2965</v>
@@ -2338,16 +2331,16 @@
         <v>2965</v>
       </c>
       <c r="M21" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O21" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P21" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
@@ -2355,31 +2348,31 @@
         <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I22" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J22" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="K22">
         <v>8108</v>
@@ -2388,19 +2381,19 @@
         <v>8108</v>
       </c>
       <c r="M22" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N22" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="O22" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P22" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Q22" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
@@ -2408,31 +2401,31 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H23" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I23" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J23" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="K23">
         <v>7060</v>
@@ -2441,16 +2434,16 @@
         <v>7060</v>
       </c>
       <c r="M23" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O23" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P23" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -2458,31 +2451,31 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I24" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J24" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="K24">
         <v>4788</v>
@@ -2491,19 +2484,19 @@
         <v>4788</v>
       </c>
       <c r="M24" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N24" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="O24" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P24" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Q24" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
@@ -2511,31 +2504,31 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F25" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J25" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="K25">
         <v>6952</v>
@@ -2544,19 +2537,19 @@
         <v>6952</v>
       </c>
       <c r="M25" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O25" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P25" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="Q25" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.3">
@@ -2564,31 +2557,31 @@
         <v>31</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I26" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="J26" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="K26">
         <v>5459</v>
@@ -2597,19 +2590,19 @@
         <v>5459</v>
       </c>
       <c r="M26" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="O26" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P26" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="Q26" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.3">
@@ -2617,31 +2610,31 @@
         <v>32</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E27" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G27" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H27" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I27" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J27" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K27">
         <v>7287</v>
@@ -2650,16 +2643,16 @@
         <v>7287</v>
       </c>
       <c r="M27" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N27" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O27" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P27" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
@@ -2667,31 +2660,31 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J28" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K28">
         <v>3375</v>
@@ -2700,19 +2693,19 @@
         <v>3375</v>
       </c>
       <c r="M28" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O28" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P28" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="Q28" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.3">
@@ -2720,31 +2713,31 @@
         <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F29" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J29" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K29">
         <v>3263</v>
@@ -2753,16 +2746,16 @@
         <v>3263</v>
       </c>
       <c r="M29" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N29" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="O29" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P29" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.3">
@@ -2770,31 +2763,31 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G30" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J30" t="s">
-        <v>229</v>
+        <v>168</v>
       </c>
       <c r="K30">
         <v>20646</v>
@@ -2803,19 +2796,19 @@
         <v>20646</v>
       </c>
       <c r="M30" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N30" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="O30" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P30" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="Q30" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
@@ -2823,28 +2816,31 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I31" t="s">
-        <v>170</v>
+        <v>168</v>
+      </c>
+      <c r="J31" t="s">
+        <v>228</v>
       </c>
       <c r="K31">
         <v>5531</v>
@@ -2853,19 +2849,19 @@
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="N31" t="s">
+        <v>263</v>
+      </c>
+      <c r="O31" t="s">
+        <v>289</v>
+      </c>
+      <c r="P31" t="s">
         <v>268</v>
       </c>
-      <c r="O31" t="s">
-        <v>294</v>
-      </c>
-      <c r="P31" t="s">
-        <v>273</v>
-      </c>
       <c r="Q31" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
@@ -2873,31 +2869,31 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E32" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" t="s">
         <v>115</v>
       </c>
-      <c r="F32" t="s">
-        <v>116</v>
-      </c>
       <c r="G32" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I32" t="s">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="J32" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="K32">
         <v>8492</v>
@@ -2906,16 +2902,16 @@
         <v>8492</v>
       </c>
       <c r="M32" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N32" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="O32" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P32" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
@@ -2923,31 +2919,31 @@
         <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I33" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="J33" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="K33">
         <v>6790</v>
@@ -2956,19 +2952,19 @@
         <v>6790</v>
       </c>
       <c r="M33" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N33" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="O33" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P33" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q33" t="s">
         <v>273</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.3">
@@ -2976,31 +2972,31 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I34" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J34" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="K34">
         <v>2323</v>
@@ -3009,16 +3005,16 @@
         <v>2323</v>
       </c>
       <c r="M34" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N34" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="O34" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="P34" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.3">
@@ -3026,31 +3022,31 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I35" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="J35" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="K35">
         <v>15438</v>
@@ -3059,16 +3055,16 @@
         <v>15438</v>
       </c>
       <c r="M35" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N35" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="O35" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P35" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.3">
@@ -3076,31 +3072,31 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F36" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H36" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I36" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="J36" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="K36">
         <v>9946</v>
@@ -3109,16 +3105,16 @@
         <v>9946</v>
       </c>
       <c r="M36" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N36" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="O36" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="P36" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
@@ -3126,31 +3122,31 @@
         <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G37" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I37" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="J37" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="K37">
         <v>1416</v>
@@ -3159,16 +3155,16 @@
         <v>1416</v>
       </c>
       <c r="M37" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N37" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="O37" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P37" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.3">
@@ -3176,28 +3172,31 @@
         <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G38" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I38" t="s">
-        <v>177</v>
+        <v>173</v>
+      </c>
+      <c r="J38" t="s">
+        <v>176</v>
       </c>
       <c r="K38">
         <v>5426</v>
@@ -3206,19 +3205,19 @@
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="N38" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="O38" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="P38" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="Q38" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
@@ -3226,31 +3225,31 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F39" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G39" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H39" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I39" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="J39" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="K39">
         <v>4644</v>
@@ -3259,19 +3258,19 @@
         <v>4644</v>
       </c>
       <c r="M39" t="s">
+        <v>255</v>
+      </c>
+      <c r="N39" t="s">
         <v>260</v>
       </c>
-      <c r="N39" t="s">
-        <v>265</v>
-      </c>
       <c r="O39" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P39" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="Q39" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
@@ -3279,31 +3278,31 @@
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" t="s">
         <v>108</v>
       </c>
-      <c r="E40" t="s">
-        <v>109</v>
-      </c>
       <c r="F40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H40" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I40" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J40" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="K40">
         <v>9097</v>
@@ -3312,19 +3311,19 @@
         <v>9097</v>
       </c>
       <c r="M40" t="s">
+        <v>255</v>
+      </c>
+      <c r="N40" t="s">
         <v>260</v>
       </c>
-      <c r="N40" t="s">
-        <v>265</v>
-      </c>
       <c r="O40" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="P40" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="Q40" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
@@ -3332,31 +3331,31 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I41" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="J41" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="K41">
         <v>4217</v>
@@ -3365,16 +3364,16 @@
         <v>4217</v>
       </c>
       <c r="M41" t="s">
+        <v>255</v>
+      </c>
+      <c r="N41" t="s">
         <v>260</v>
       </c>
-      <c r="N41" t="s">
-        <v>265</v>
-      </c>
       <c r="O41" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P41" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.3">
@@ -3382,31 +3381,31 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D42" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I42" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="J42" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="K42">
         <v>1408</v>
@@ -3415,19 +3414,19 @@
         <v>1408</v>
       </c>
       <c r="M42" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N42" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="O42" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P42" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="Q42" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
@@ -3435,31 +3434,31 @@
         <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E43" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F43" t="s">
+        <v>129</v>
+      </c>
+      <c r="G43" t="s">
         <v>130</v>
       </c>
-      <c r="G43" t="s">
-        <v>131</v>
-      </c>
       <c r="H43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I43" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="J43" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="K43">
         <v>7325</v>
@@ -3468,19 +3467,19 @@
         <v>7325</v>
       </c>
       <c r="M43" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O43" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P43" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q43" t="s">
         <v>273</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
@@ -3488,31 +3487,31 @@
         <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I44" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="J44" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="K44">
         <v>1011</v>
@@ -3521,16 +3520,16 @@
         <v>573</v>
       </c>
       <c r="M44" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="N44" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="O44" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P44" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
@@ -3538,31 +3537,31 @@
         <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D45" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G45" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I45" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J45" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="K45">
         <v>7468</v>
@@ -3571,19 +3570,19 @@
         <v>7468</v>
       </c>
       <c r="M45" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N45" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="O45" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P45" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="Q45" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
@@ -3591,31 +3590,31 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F46" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I46" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="J46" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="K46">
         <v>2032</v>
@@ -3624,16 +3623,16 @@
         <v>2032</v>
       </c>
       <c r="M46" t="s">
+        <v>255</v>
+      </c>
+      <c r="N46" t="s">
         <v>260</v>
       </c>
-      <c r="N46" t="s">
+      <c r="O46" t="s">
+        <v>285</v>
+      </c>
+      <c r="P46" t="s">
         <v>265</v>
-      </c>
-      <c r="O46" t="s">
-        <v>290</v>
-      </c>
-      <c r="P46" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
@@ -3641,31 +3640,31 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F47" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G47" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H47" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I47" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J47" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="K47">
         <v>4165</v>
@@ -3674,19 +3673,19 @@
         <v>4165</v>
       </c>
       <c r="M47" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N47" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O47" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="P47" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="Q47" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
@@ -3694,31 +3693,31 @@
         <v>39</v>
       </c>
       <c r="B48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H48" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I48" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="J48" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="K48">
         <v>1366</v>
@@ -3727,19 +3726,19 @@
         <v>1366</v>
       </c>
       <c r="M48" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N48" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O48" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="P48" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="Q48" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
@@ -3747,31 +3746,31 @@
         <v>40</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D49" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F49" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G49" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H49" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I49" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J49" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="K49">
         <v>1285</v>
@@ -3780,19 +3779,19 @@
         <v>1285</v>
       </c>
       <c r="M49" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N49" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="O49" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P49" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="Q49" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
@@ -3800,31 +3799,31 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C50" t="s">
+        <v>102</v>
+      </c>
+      <c r="D50" t="s">
         <v>103</v>
       </c>
-      <c r="D50" t="s">
-        <v>104</v>
-      </c>
       <c r="E50" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H50" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I50" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J50" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="K50">
         <v>7936</v>
@@ -3833,19 +3832,19 @@
         <v>7936</v>
       </c>
       <c r="M50" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N50" t="s">
+        <v>264</v>
+      </c>
+      <c r="O50" t="s">
+        <v>290</v>
+      </c>
+      <c r="P50" t="s">
         <v>269</v>
       </c>
-      <c r="O50" t="s">
-        <v>295</v>
-      </c>
-      <c r="P50" t="s">
+      <c r="Q50" t="s">
         <v>274</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
@@ -3853,31 +3852,31 @@
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F51" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H51" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I51" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J51" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="K51">
         <v>17244</v>
@@ -3886,19 +3885,19 @@
         <v>17244</v>
       </c>
       <c r="M51" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N51" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="O51" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P51" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Q51" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
@@ -3906,31 +3905,31 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D52" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F52" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G52" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H52" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I52" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J52" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="K52">
         <v>11381</v>
@@ -3939,16 +3938,16 @@
         <v>11381</v>
       </c>
       <c r="M52" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N52" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="O52" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="P52" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
@@ -3956,31 +3955,31 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D53" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F53" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H53" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I53" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J53" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K53">
         <v>8664</v>
@@ -3989,19 +3988,19 @@
         <v>8664</v>
       </c>
       <c r="M53" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N53" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="O53" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="P53" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q53" t="s">
         <v>275</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
@@ -4009,31 +4008,31 @@
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H54" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I54" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J54" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="K54">
         <v>7757</v>
@@ -4042,16 +4041,16 @@
         <v>7757</v>
       </c>
       <c r="M54" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O54" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="P54" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.3">
@@ -4059,31 +4058,31 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D55" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E55" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G55" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H55" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I55" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="J55" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="K55">
         <v>468</v>
@@ -4092,19 +4091,19 @@
         <v>468</v>
       </c>
       <c r="M55" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N55" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O55" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P55" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="Q55" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
@@ -4112,31 +4111,31 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F56" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G56" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H56" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I56" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="J56" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="K56">
         <v>1176</v>
@@ -4145,19 +4144,19 @@
         <v>1176</v>
       </c>
       <c r="M56" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N56" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O56" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P56" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Q56" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
@@ -4165,31 +4164,31 @@
         <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C57" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E57" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F57" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G57" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H57" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I57" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="J57" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K57">
         <v>11752</v>
@@ -4198,19 +4197,19 @@
         <v>11752</v>
       </c>
       <c r="M57" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N57" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="O57" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="P57" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="Q57" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.3">
@@ -4218,31 +4217,31 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D58" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E58" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F58" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G58" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I58" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J58" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="K58">
         <v>9667</v>
@@ -4251,19 +4250,19 @@
         <v>9667</v>
       </c>
       <c r="M58" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N58" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="O58" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="P58" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="Q58" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
@@ -4271,31 +4270,31 @@
         <v>50</v>
       </c>
       <c r="B59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E59" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F59" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G59" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H59" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I59" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="J59" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="K59">
         <v>5109</v>
@@ -4304,16 +4303,16 @@
         <v>5109</v>
       </c>
       <c r="M59" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N59" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O59" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="P59" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
@@ -4321,31 +4320,31 @@
         <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C60" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" t="s">
         <v>103</v>
       </c>
-      <c r="D60" t="s">
-        <v>104</v>
-      </c>
       <c r="E60" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F60" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G60" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H60" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I60" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="J60" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="K60">
         <v>5284</v>
@@ -4354,16 +4353,16 @@
         <v>5284</v>
       </c>
       <c r="M60" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N60" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="O60" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="P60" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.3">
@@ -4371,31 +4370,31 @@
         <v>58</v>
       </c>
       <c r="B61" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C61" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F61" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G61" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H61" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I61" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="J61" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="K61">
         <v>9092</v>
@@ -4404,19 +4403,19 @@
         <v>9092</v>
       </c>
       <c r="M61" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="N61" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O61" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P61" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="Q61" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
@@ -4424,31 +4423,31 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C62" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F62" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H62" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I62" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J62" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="K62">
         <v>801</v>
@@ -4457,22 +4456,23 @@
         <v>801</v>
       </c>
       <c r="M62" t="s">
+        <v>255</v>
+      </c>
+      <c r="N62" t="s">
         <v>260</v>
       </c>
-      <c r="N62" t="s">
-        <v>265</v>
-      </c>
       <c r="O62" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P62" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q62" t="s">
         <v>273</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>278</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>